--- a/cuadros/JUNIO/BARQUISIMETO.xlsx
+++ b/cuadros/JUNIO/BARQUISIMETO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +555,76 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>ID_20260601154001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BARQUISIMETO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>300018955</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>REIDINSON MONTERO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SE DUPLICO EL SKU DEL LIMON Y FALTO AGREGAR EL SKU DEL AGUACATE </t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>INC_153735_0.jpeg INC_153735_1.jpeg</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ID_20260602153735</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/BARQUISIMETO.xlsx
+++ b/cuadros/JUNIO/BARQUISIMETO.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>INC_153735_0.jpeg INC_153735_1.jpeg</t>
+          <t>INC_153735_0.jpeg</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">

--- a/cuadros/JUNIO/BARQUISIMETO.xlsx
+++ b/cuadros/JUNIO/BARQUISIMETO.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>INC_154001_0.jpeg INC_154001_1.jpeg</t>
+          <t>INC_154001_1.jpeg</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">

--- a/cuadros/JUNIO/BARQUISIMETO.xlsx
+++ b/cuadros/JUNIO/BARQUISIMETO.xlsx
@@ -547,11 +547,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>INC_154001_1.jpeg</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>ID_20260601154001</t>

--- a/cuadros/JUNIO/BARQUISIMETO.xlsx
+++ b/cuadros/JUNIO/BARQUISIMETO.xlsx
@@ -613,11 +613,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>INC_153735_0.jpeg</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>ID_20260602153735</t>

--- a/cuadros/JUNIO/BARQUISIMETO.xlsx
+++ b/cuadros/JUNIO/BARQUISIMETO.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -414,7 +413,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
+  <cols>
+    <col width="25.921875" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -479,12 +481,12 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>FOTO_INCIDENCIA</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ID</t>
         </is>
       </c>
     </row>
@@ -547,8 +549,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>ID_20260601154001</t>
         </is>
@@ -613,8 +614,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>ID_20260602153735</t>
         </is>

--- a/cuadros/JUNIO/BARQUISIMETO.xlsx
+++ b/cuadros/JUNIO/BARQUISIMETO.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -49,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -412,11 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
-  <cols>
-    <col width="25.921875" customWidth="1" min="12" max="12"/>
-  </cols>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -617,6 +615,76 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>ID_20260602153735</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BARQUISIMETO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ADOLFO'S VICAR C.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>13844</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>RUBER RAMOS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NRO DE FACTURA ERRADO</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ID_20260603133203</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>INC_133203_0.jpeg INC_133203_1.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/BARQUISIMETO.xlsx
+++ b/cuadros/JUNIO/BARQUISIMETO.xlsx
@@ -561,17 +561,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CAVA LUXOR</t>
+          <t>ADOLFO'S VICAR C.A.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>300018955</t>
+          <t>13844</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -581,22 +581,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>REIDINSON MONTERO</t>
+          <t>RUBER RAMOS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>PRODUCTO O SKU DUPLICADO.</t>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO A</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SE DUPLICO EL SKU DEL LIMON Y FALTO AGREGAR EL SKU DEL AGUACATE </t>
+          <t>NRO DE FACTURA ERRADO</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -614,7 +614,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ID_20260602153735</t>
+          <t>ID_20260603133203</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>INC_133203_0.jpeg INC_133203_1.png</t>
         </is>
       </c>
     </row>
@@ -626,17 +631,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADOLFO'S VICAR C.A.</t>
+          <t>CAVA LUXOR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>300018955</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -646,22 +651,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RUBER RAMOS</t>
+          <t>REIDINSON MONTERO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TIPO A</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NRO DE FACTURA ERRADO</t>
+          <t xml:space="preserve">SE DUPLICO EL SKU DEL LIMON Y FALTO AGREGAR EL SKU DEL AGUACATE </t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -679,12 +684,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ID_20260603133203</t>
+          <t>ID_20260602153735</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>INC_133203_0.jpeg INC_133203_1.png</t>
+          <t>INC_142535_0.jpeg INC_142535_1.jpeg</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/BARQUISIMETO.xlsx
+++ b/cuadros/JUNIO/BARQUISIMETO.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,8 +412,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -501,37 +500,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>36682</t>
+          <t>13844</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DEVOLUCION</t>
+          <t>RECEPCION</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>REIDINSON MONTERO</t>
+          <t>RUBER RAMOS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ERROR DE KG EN TARA.</t>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>TIPO C</t>
+          <t>TIPO A</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SE COLOCO TARA A LA MORA PERO SE RECIBE POR BANDEJA </t>
+          <t>NRO DE FACTURA ERRADO</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -549,10 +548,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>ID_20260601154001</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>ID_20260603133203</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>INC_133203_0.jpeg INC_133203_1.png</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -562,17 +565,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADOLFO'S VICAR C.A.</t>
+          <t>CAVA LUXOR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>300018955</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -582,22 +585,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RUBER RAMOS</t>
+          <t>REIDINSON MONTERO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>TIPO A</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NRO DE FACTURA ERRADO</t>
+          <t xml:space="preserve">SE DUPLICO EL SKU DEL LIMON Y FALTO AGREGAR EL SKU DEL AGUACATE </t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -615,80 +618,10 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ID_20260603133203</t>
+          <t>ID_20260602153735</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
-        <is>
-          <t>INC_133203_0.jpeg INC_133203_1.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BARQUISIMETO</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CAVA LUXOR</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>300018955</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>RECEPCION</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>REIDINSON MONTERO</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>PRODUCTO O SKU DUPLICADO.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>TIPO B</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SE DUPLICO EL SKU DEL LIMON Y FALTO AGREGAR EL SKU DEL AGUACATE </t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>SIN_FOTO</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>NINGUNA</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>ID_20260602153735</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
         <is>
           <t>INC_142535_0.jpeg INC_142535_1.jpeg</t>
         </is>

--- a/cuadros/JUNIO/BARQUISIMETO.xlsx
+++ b/cuadros/JUNIO/BARQUISIMETO.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -49,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -412,8 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -624,6 +625,76 @@
       <c r="N3" t="inlineStr">
         <is>
           <t>INC_142535_0.jpeg INC_142535_1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BARQUISIMETO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ADOLFO'S VICAR C.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>36682</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>REIDINSON MONTERO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SE LE CARGO TARA A LA MORA, PERO ESE PRODUCTO SE CONTABILIZA POR UND DE BANDEJAS </t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ID_20260603144033</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>INC_144033_0.jpeg INC_144033_1.jpeg</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/BARQUISIMETO.xlsx
+++ b/cuadros/JUNIO/BARQUISIMETO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,6 +695,76 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>INC_144033_0.jpeg INC_144033_1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BARQUISIMETO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>300019135</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>REIDINSON MONTERO</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NO SE INDICÓ DIFERENCIA AL DORSO DE LA FACTURA.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ERROR EN LA NOTA AL DORSO</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ID_20260605152639</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>INC_152639_0.jpeg INC_152639_1.jpg</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/BARQUISIMETO.xlsx
+++ b/cuadros/JUNIO/BARQUISIMETO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -765,6 +765,76 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>INC_152639_0.jpeg INC_152639_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BARQUISIMETO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>KC GLOBAL INT, C.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6622</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>REIDINSON MONTERO</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>NRO DE CONTROL ERRADO</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ID_20260606100315</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>INC_100315_0.jpeg INC_100315_1.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/BARQUISIMETO.xlsx
+++ b/cuadros/JUNIO/BARQUISIMETO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,6 +835,76 @@
       <c r="N6" t="inlineStr">
         <is>
           <t>INC_100315_0.jpeg INC_100315_1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BARQUISIMETO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ALIMENTOS DIFRESCA, C.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>610213155</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>REIDINSON MONTERO</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SE DUPLICO EL SKU DE SALSA KETCHUP C/DIABLITO 380 GR</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ID_20260608121350</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>INC_121350_0.png INC_121350_1.jpeg</t>
         </is>
       </c>
     </row>
